--- a/Result/profitability/3685.xlsx
+++ b/Result/profitability/3685.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1475</v>
+        <v>-0.12125</v>
       </c>
       <c r="N2" t="n">
-        <v>20.2625</v>
+        <v>21.02875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.06625</v>
+        <v>-0.0325</v>
       </c>
       <c r="N3" t="n">
-        <v>24.20625</v>
+        <v>25.47</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05</v>
+        <v>0.08375</v>
       </c>
       <c r="N4" t="n">
-        <v>20.62125</v>
+        <v>21.06375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.58</v>
       </c>
       <c r="M5" t="n">
-        <v>0.14125</v>
+        <v>0.22125</v>
       </c>
       <c r="N5" t="n">
-        <v>26.08</v>
+        <v>26.61625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0.30625</v>
+        <v>0.315</v>
       </c>
       <c r="N6" t="n">
-        <v>30.005</v>
+        <v>30.32125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.72</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0.455</v>
       </c>
       <c r="N7" t="n">
-        <v>33.54875</v>
+        <v>33.69125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.54</v>
+        <v>0.5425</v>
       </c>
       <c r="N8" t="n">
-        <v>36.335</v>
+        <v>36.35125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.84</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.6325</v>
       </c>
       <c r="N9" t="n">
         <v>39.00750000000001</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3685</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>367</v>
+      </c>
+      <c r="D71" t="n">
+        <v>281</v>
+      </c>
+      <c r="E71" t="n">
+        <v>86</v>
+      </c>
+      <c r="F71" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="G71" t="n">
+        <v>40</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>39</v>
+      </c>
+      <c r="K71" t="n">
+        <v>9</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="N71" t="n">
+        <v>19.97625</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.01999999999999999</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.1300000000000026</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.005572224603514808</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-1.230769230769231</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>4.289999999999999</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0.2237871674491392</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
